--- a/신청서/[기관별신청목록]_정읍우체국.xlsx
+++ b/신청서/[기관별신청목록]_정읍우체국.xlsx
@@ -921,7 +921,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>010-2662-9704</t>
+          <t>010-0000-0000(제출본에만 기재)</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>010-2662-9704</t>
+          <t>010-0000-0000(제출본에만 기재)</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
